--- a/data/trans_orig/IP07A17-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07A17-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar con todos sus amigos en 2007 (tasa de respuesta: 98,3%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el adulto en 2007 (tasa de respuesta: 98,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10848</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8783</t>
+          <t>8578</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18224</t>
+          <t>18812</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>35,44%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13534</t>
+          <t>13335</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10852</t>
+          <t>10633</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19795</t>
+          <t>19532</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18449</t>
+          <t>19156</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30270</t>
+          <t>30407</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,28%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2420</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8588</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>13422</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9400</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19916</t>
+          <t>19647</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,01%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3431</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25934</t>
+          <t>25883</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35705</t>
+          <t>35726</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42030</t>
+          <t>41080</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51075</t>
+          <t>51031</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71348</t>
+          <t>70799</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85167</t>
+          <t>84349</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,13%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16450</t>
+          <t>16235</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11364</t>
+          <t>11350</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24600</t>
+          <t>24870</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7093</t>
+          <t>7117</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>4523</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11807</t>
+          <t>11193</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21729</t>
+          <t>20970</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9141</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17286</t>
+          <t>17790</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36221</t>
+          <t>36518</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>56,41%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10128</t>
+          <t>10142</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20085</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11058</t>
+          <t>10679</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19241</t>
+          <t>18851</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24523</t>
+          <t>23852</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38059</t>
+          <t>36769</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>56,8%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>746</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9640</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12641</t>
+          <t>12678</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23206</t>
+          <t>22836</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11650</t>
+          <t>11692</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21442</t>
+          <t>21567</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26558</t>
+          <t>27310</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41108</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,77%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>13011</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23184</t>
+          <t>23028</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14807</t>
+          <t>14851</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25040</t>
+          <t>25156</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>30805</t>
+          <t>30727</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>45762</t>
+          <t>45083</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>58,03%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>584</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>5669</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10290</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7557</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>15072</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14762</t>
+          <t>15411</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17381</t>
+          <t>17741</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>27653</t>
+          <t>27868</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>68,04%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11079</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>5727</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14164</t>
+          <t>13496</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11971</t>
+          <t>11806</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22199</t>
+          <t>21689</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>52,95%</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>17494</t>
+          <t>16757</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>16475</t>
+          <t>16457</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>19007</t>
+          <t>19233</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>30948</t>
+          <t>31397</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,88%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>6611</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15073</t>
+          <t>14748</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10668</t>
+          <t>10251</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18964</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>19595</t>
+          <t>19699</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>31807</t>
+          <t>31255</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>6745</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>7248</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11609</t>
+          <t>11871</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>24953</t>
+          <t>25068</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>37057</t>
+          <t>37435</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>23653</t>
+          <t>22639</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>35888</t>
+          <t>35562</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>51794</t>
+          <t>51567</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>69791</t>
+          <t>69091</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,08%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>13583</t>
+          <t>14027</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>25362</t>
+          <t>25873</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>21956</t>
+          <t>22559</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>34027</t>
+          <t>34485</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>38459</t>
+          <t>38913</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>56202</t>
+          <t>56350</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,19%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>7520</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>7989</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>12895</t>
+          <t>13054</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3668</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>23961</t>
+          <t>24140</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>37246</t>
+          <t>37385</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>24800</t>
+          <t>24804</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>37738</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>52551</t>
+          <t>51505</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>70221</t>
+          <t>70699</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,71%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>29062</t>
+          <t>28675</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>43123</t>
+          <t>42453</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>26668</t>
+          <t>27315</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>40079</t>
+          <t>39625</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>59795</t>
+          <t>59538</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>78864</t>
+          <t>78597</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>12432</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>9879</t>
+          <t>9346</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7065</t>
+          <t>7344</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>17889</t>
+          <t>17568</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>6065</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>143677</t>
+          <t>143213</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>172006</t>
+          <t>171182</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>149801</t>
+          <t>152519</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>181093</t>
+          <t>182295</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>305050</t>
+          <t>304942</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>344854</t>
+          <t>344240</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,38%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>113145</t>
+          <t>113682</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>140461</t>
+          <t>141886</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>128459</t>
+          <t>127169</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>158308</t>
+          <t>157582</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>249463</t>
+          <t>248856</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>288571</t>
+          <t>289981</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>44,12%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>18702</t>
+          <t>18580</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>35177</t>
+          <t>34398</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>20323</t>
+          <t>20677</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>37004</t>
+          <t>36560</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>43777</t>
+          <t>43999</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>66166</t>
+          <t>66589</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>7722</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>10854</t>
+          <t>10641</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>776</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar con todos sus amigos en 2012 (tasa de respuesta: 97,39%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el adulto en 2012 (tasa de respuesta: 97,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>14708</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21521</t>
+          <t>21475</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16026</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24566</t>
+          <t>24396</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33347</t>
+          <t>33090</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44989</t>
+          <t>44266</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>80,83%</t>
         </is>
       </c>
     </row>
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10477</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13669</t>
+          <t>14159</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>5568</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>955</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6954</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10113</t>
+          <t>10486</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27895</t>
+          <t>28494</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38327</t>
+          <t>38698</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34924</t>
+          <t>34946</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44974</t>
+          <t>45545</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66709</t>
+          <t>66410</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81399</t>
+          <t>81216</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,06%</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13249</t>
+          <t>13382</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16863</t>
+          <t>17370</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13407</t>
+          <t>13953</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27144</t>
+          <t>27858</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>672</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7895</t>
+          <t>7739</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4662</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13964</t>
+          <t>13172</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21249</t>
+          <t>21212</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12520</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21238</t>
+          <t>21624</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28567</t>
+          <t>28386</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40364</t>
+          <t>40280</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,3%</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>11453</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9170</t>
+          <t>9053</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18387</t>
+          <t>18208</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15094</t>
+          <t>15195</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26428</t>
+          <t>27184</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>47,45%</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8716,44 +8716,44 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>14,85%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1396</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>4368</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
           <t>13,75%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>1396</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>4299</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>13,53%</t>
-        </is>
-      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>3</t>
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5652</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9152,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9963</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20045</t>
+          <t>19947</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13730</t>
+          <t>13788</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23321</t>
+          <t>24014</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26646</t>
+          <t>26481</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40236</t>
+          <t>40995</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>57,04%</t>
         </is>
       </c>
     </row>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14885</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25071</t>
+          <t>25113</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19966</t>
+          <t>19974</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>27696</t>
+          <t>27993</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>42138</t>
+          <t>42004</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,44%</t>
         </is>
       </c>
     </row>
@@ -9383,7 +9383,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>692</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7995</t>
+          <t>7857</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5214</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12798</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9272</t>
+          <t>9315</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>15993</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>16586</t>
+          <t>16714</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>27147</t>
+          <t>27152</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,6%</t>
         </is>
       </c>
     </row>
@@ -9947,12 +9947,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13085</t>
+          <t>13214</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>9465</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9997,47 +9997,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t>46,96%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>14913</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>10072</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>20383</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>36,58%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>24,71%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>50,0%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>14913</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>9707</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>19981</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>36,58%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>23,81%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>49,01%</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>895</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>6896</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>11039</t>
+          <t>10604</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>20379</t>
+          <t>19875</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>16758</t>
+          <t>16955</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>22376</t>
+          <t>22209</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>34193</t>
+          <t>34023</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,51%</t>
         </is>
       </c>
     </row>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15833</t>
+          <t>16466</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>8023</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>16376</t>
+          <t>16615</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>17325</t>
+          <t>17517</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>29957</t>
+          <t>29604</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>53,52%</t>
         </is>
       </c>
     </row>
@@ -10742,12 +10742,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>474</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10757,12 +10757,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>715</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10930,7 +10930,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>23910</t>
+          <t>23935</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>36414</t>
+          <t>36480</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11233,12 +11233,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>25743</t>
+          <t>25613</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>38144</t>
+          <t>37740</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>54515</t>
+          <t>53784</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>71669</t>
+          <t>70989</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>63,74%</t>
         </is>
       </c>
     </row>
@@ -11311,12 +11311,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>16674</t>
+          <t>16680</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>28920</t>
+          <t>29141</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>12544</t>
+          <t>12810</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>24165</t>
+          <t>24033</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>32211</t>
+          <t>32177</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>49073</t>
+          <t>48790</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11396,12 +11396,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,81%</t>
         </is>
       </c>
     </row>
@@ -11424,12 +11424,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11439,12 +11439,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>8281</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>4051</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>13249</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11705,7 +11705,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>3247</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>17633</t>
+          <t>17699</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>31491</t>
+          <t>30340</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,12 +11895,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>17251</t>
+          <t>17108</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>30022</t>
+          <t>29950</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>38162</t>
+          <t>38009</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>56958</t>
+          <t>56521</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,8%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>37463</t>
+          <t>37821</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>51789</t>
+          <t>51579</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>35842</t>
+          <t>36033</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>50020</t>
+          <t>50684</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>76993</t>
+          <t>78282</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>97957</t>
+          <t>98265</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,24%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>14345</t>
+          <t>13770</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>14618</t>
+          <t>14770</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>12447</t>
+          <t>12490</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>25471</t>
+          <t>25768</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>9277</t>
+          <t>10400</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>149047</t>
+          <t>148993</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>178784</t>
+          <t>177753</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>163386</t>
+          <t>162006</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>193089</t>
+          <t>191181</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>320082</t>
+          <t>320716</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>363289</t>
+          <t>364353</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>56,1%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>112005</t>
+          <t>110896</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>141238</t>
+          <t>140418</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>108979</t>
+          <t>111806</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>138869</t>
+          <t>139177</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>232619</t>
+          <t>230053</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>271327</t>
+          <t>271028</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,73%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>15703</t>
+          <t>16158</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>32253</t>
+          <t>32227</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,7 +12803,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>15279</t>
+          <t>16184</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>31105</t>
+          <t>30314</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>35303</t>
+          <t>34678</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>57558</t>
+          <t>57100</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12951,12 +12951,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>15194</t>
+          <t>15723</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -13014,12 +13014,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>591</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13029,12 +13029,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13084,12 +13084,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar con todos sus amigos en 2016 (tasa de respuesta: 97,64%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el adulto en 2016 (tasa de respuesta: 97,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17992</t>
+          <t>18281</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25917</t>
+          <t>25999</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8427</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17649</t>
+          <t>16746</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13530,12 +13530,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28284</t>
+          <t>28318</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40526</t>
+          <t>40727</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>70,42%</t>
         </is>
       </c>
     </row>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8759</t>
+          <t>8922</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>8311</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17215</t>
+          <t>17668</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12075</t>
+          <t>11984</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24292</t>
+          <t>23539</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>40,7%</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13746,7 +13746,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13761,7 +13761,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>547</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13854,12 +13854,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13869,12 +13869,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13889,12 +13889,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>878</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7386</t>
+          <t>7168</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13904,12 +13904,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30768</t>
+          <t>30811</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41810</t>
+          <t>41983</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36376</t>
+          <t>36596</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47763</t>
+          <t>47812</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71094</t>
+          <t>70989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86747</t>
+          <t>87010</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14247,12 +14247,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,52%</t>
         </is>
       </c>
     </row>
@@ -14275,12 +14275,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8933</t>
+          <t>9269</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20205</t>
+          <t>20055</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14290,12 +14290,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7989</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18491</t>
+          <t>18636</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19646</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34607</t>
+          <t>34949</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,54%</t>
         </is>
       </c>
     </row>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14423,12 +14423,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>651</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14438,12 +14438,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14473,12 +14473,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14556,7 +14556,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14689,7 +14689,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20192</t>
+          <t>20053</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29385</t>
+          <t>29507</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11589</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21191</t>
+          <t>21274</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14894,12 +14894,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35428</t>
+          <t>34798</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49129</t>
+          <t>49206</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14929,12 +14929,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,38%</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13531</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14972,12 +14972,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14992,12 +14992,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15149</t>
+          <t>14768</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12514</t>
+          <t>12797</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25729</t>
+          <t>26276</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>38,65%</t>
         </is>
       </c>
     </row>
@@ -15105,12 +15105,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9532</t>
+          <t>10111</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15120,12 +15120,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9930</t>
+          <t>9837</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15155,12 +15155,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -15301,7 +15301,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15316,7 +15316,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15336,7 +15336,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15386,7 +15386,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23720</t>
+          <t>23155</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32954</t>
+          <t>32756</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15541,12 +15541,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25487</t>
+          <t>25119</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35246</t>
+          <t>35433</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51399</t>
+          <t>51766</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65237</t>
+          <t>65183</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,71%</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12624</t>
+          <t>13028</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11603</t>
+          <t>11607</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9726</t>
+          <t>9953</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21085</t>
+          <t>21866</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>27,08%</t>
         </is>
       </c>
     </row>
@@ -15787,12 +15787,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>760</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>6609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>756</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>7198</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15900,12 +15900,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>632</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15915,12 +15915,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15935,12 +15935,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>788</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6960</t>
+          <t>6831</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15950,12 +15950,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -15983,7 +15983,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4924</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -15998,7 +15998,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -16208,12 +16208,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16223,12 +16223,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>12769</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>7544</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>17008</t>
+          <t>17077</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,15%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10293</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16791</t>
+          <t>16964</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>9068</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17456</t>
+          <t>17638</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>21955</t>
+          <t>21577</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32431</t>
+          <t>32369</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,32%</t>
         </is>
       </c>
     </row>
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>624</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16449,12 +16449,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16469,12 +16469,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>670</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16484,12 +16484,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>9330</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -16700,7 +16700,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3621</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16715,7 +16715,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16750,7 +16750,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14803</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>22945</t>
+          <t>22988</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16925,12 +16925,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14912</t>
+          <t>15010</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>24119</t>
+          <t>24046</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16940,12 +16940,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>32510</t>
+          <t>32848</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>45098</t>
+          <t>45052</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,11%</t>
         </is>
       </c>
     </row>
@@ -17003,12 +17003,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>4996</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13045</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17038,12 +17038,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11631</t>
+          <t>11367</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17053,12 +17053,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>10174</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>21916</t>
+          <t>21640</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,56%</t>
         </is>
       </c>
     </row>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>2863</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>6061</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>686</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17397,7 +17397,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4509</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -17572,12 +17572,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>22564</t>
+          <t>23059</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>35322</t>
+          <t>35667</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17587,12 +17587,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17607,12 +17607,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>25346</t>
+          <t>25151</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>37987</t>
+          <t>38033</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>51196</t>
+          <t>51272</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>70873</t>
+          <t>69896</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,12%</t>
         </is>
       </c>
     </row>
@@ -17685,12 +17685,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>25413</t>
+          <t>25512</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>38911</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>20488</t>
+          <t>20492</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>33075</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17740,7 +17740,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>48216</t>
+          <t>49626</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>67404</t>
+          <t>67536</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17770,12 +17770,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,32%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>12393</t>
+          <t>12207</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>9620</t>
+          <t>9828</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17848,12 +17848,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>7172</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>18639</t>
+          <t>18152</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -17951,7 +17951,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17986,7 +17986,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>24567</t>
+          <t>24562</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>38665</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>31295</t>
+          <t>31100</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>45785</t>
+          <t>46095</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18304,12 +18304,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>59806</t>
+          <t>59608</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>80014</t>
+          <t>79490</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,33%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>32846</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>47075</t>
+          <t>47206</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>22172</t>
+          <t>21246</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>35756</t>
+          <t>35620</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>58286</t>
+          <t>59329</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>78393</t>
+          <t>79041</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>51,04%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>12438</t>
+          <t>12325</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>11008</t>
+          <t>10683</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>20073</t>
+          <t>20791</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -18598,7 +18598,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18633,7 +18633,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -18668,7 +18668,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18683,7 +18683,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -18746,7 +18746,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4883</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -18761,7 +18761,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -18781,7 +18781,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>180801</t>
+          <t>181307</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>211375</t>
+          <t>211832</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18951,12 +18951,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>184981</t>
+          <t>185812</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>215282</t>
+          <t>216843</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>373874</t>
+          <t>373451</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>419120</t>
+          <t>420754</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,45%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>114830</t>
+          <t>116219</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>144470</t>
+          <t>145909</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>103881</t>
+          <t>102355</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>132224</t>
+          <t>130885</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>225974</t>
+          <t>224757</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>268154</t>
+          <t>269772</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>14322</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>28560</t>
+          <t>28857</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>19079</t>
+          <t>18576</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>35387</t>
+          <t>35018</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>36872</t>
+          <t>37595</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>59589</t>
+          <t>59272</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>8701</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19290,12 +19290,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>12664</t>
+          <t>11926</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19325,12 +19325,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>17934</t>
+          <t>18016</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19360,12 +19360,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -19388,12 +19388,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>656</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19403,12 +19403,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19423,12 +19423,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19438,12 +19438,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19473,12 +19473,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
